--- a/data/predictions.xlsx
+++ b/data/predictions.xlsx
@@ -448,11 +448,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CUST_0189</t>
+          <t>CUST_0197</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6298999786376953</v>
+        <v>0.961899995803833</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -461,11 +461,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CUST_0485</t>
+          <t>CUST_0189</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6298999786376953</v>
+        <v>0.9514999985694885</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -474,11 +474,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CUST_1180</t>
+          <t>CUST_0505</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6115999817848206</v>
+        <v>0.9387000203132629</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -487,11 +487,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CUST_0505</t>
+          <t>CUST_0606</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6046000123023987</v>
+        <v>0.9337000250816345</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -500,11 +500,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUST_0126</t>
+          <t>CUST_0180</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5989000201225281</v>
+        <v>0.7928000092506409</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -513,11 +513,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUST_0197</t>
+          <t>CUST_0440</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5964999794960022</v>
+        <v>0.7666000127792358</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CUST_0963</t>
+          <t>CUST_0237</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5953999757766724</v>
+        <v>0.7555999755859375</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -539,11 +539,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUST_0714</t>
+          <t>CUST_0963</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5949000120162964</v>
+        <v>0.7332000136375427</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -552,11 +552,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CUST_0440</t>
+          <t>CUST_0077</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5928999781608582</v>
+        <v>0.732699990272522</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -565,11 +565,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CUST_0091</t>
+          <t>CUST_0126</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5893999934196472</v>
+        <v>0.7276999950408936</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -578,11 +578,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUST_0185</t>
+          <t>CUST_0485</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5857999920845032</v>
+        <v>0.7232000231742859</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -591,11 +591,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CUST_0235</t>
+          <t>CUST_0439</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5853000283241272</v>
+        <v>0.7063999772071838</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -604,11 +604,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CUST_0237</t>
+          <t>CUST_1175</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5853000283241272</v>
+        <v>0.6955000162124634</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -617,11 +617,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CUST_0786</t>
+          <t>CUST_0947</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5853000283241272</v>
+        <v>0.6711999773979187</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -630,11 +630,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CUST_0439</t>
+          <t>CUST_0179</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5853000283241272</v>
+        <v>0.6538000106811523</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -643,11 +643,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CUST_0045</t>
+          <t>CUST_0091</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5759999752044678</v>
+        <v>0.6335999965667725</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -656,11 +656,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CUST_0207</t>
+          <t>CUST_0786</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5716999769210815</v>
+        <v>0.6295999884605408</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -669,11 +669,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CUST_0013</t>
+          <t>CUST_1189</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5715000033378601</v>
+        <v>0.617900013923645</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -682,11 +682,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CUST_1189</t>
+          <t>CUST_1055</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5687000155448914</v>
+        <v>0.6169000267982483</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -695,11 +695,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CUST_0006</t>
+          <t>CUST_0868</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5615000128746033</v>
+        <v>0.6067000031471252</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -708,11 +708,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CUST_0180</t>
+          <t>CUST_0185</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5609999895095825</v>
+        <v>0.5705999732017517</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -721,11 +721,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUST_1055</t>
+          <t>CUST_0261</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5586000084877014</v>
+        <v>0.5486999750137329</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -734,11 +734,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CUST_0606</t>
+          <t>CUST_0235</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5580000281333923</v>
+        <v>0.4912000000476837</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -747,11 +747,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CUST_0077</t>
+          <t>CUST_0914</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5557000041007996</v>
+        <v>0.4778000116348267</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -760,11 +760,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CUST_1175</t>
+          <t>CUST_1077</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.555400013923645</v>
+        <v>0.4541000127792358</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -773,11 +773,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CUST_1077</t>
+          <t>CUST_1008</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5533000230789185</v>
+        <v>0.4370000064373016</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -786,11 +786,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CUST_1008</t>
+          <t>CUST_0279</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5512999892234802</v>
+        <v>0.4302000105381012</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -799,11 +799,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CUST_0947</t>
+          <t>CUST_0861</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5496000051498413</v>
+        <v>0.4185999929904938</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -812,11 +812,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CUST_0754</t>
+          <t>CUST_0691</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5496000051498413</v>
+        <v>0.3977999985218048</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -825,11 +825,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CUST_0682</t>
+          <t>CUST_0714</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5407999753952026</v>
+        <v>0.390500009059906</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5393000245094299</v>
+        <v>0.3776000142097473</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -851,11 +851,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CUST_0138</t>
+          <t>CUST_0006</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5375999808311462</v>
+        <v>0.3653999865055084</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -864,11 +864,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CUST_0018</t>
+          <t>CUST_1026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5367000102996826</v>
+        <v>0.3589999973773956</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -877,11 +877,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CUST_0894</t>
+          <t>CUST_0264</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5367000102996826</v>
+        <v>0.3486999869346619</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -890,11 +890,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CUST_0528</t>
+          <t>CUST_0754</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5343999862670898</v>
+        <v>0.3357999920845032</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -903,11 +903,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CUST_0264</t>
+          <t>CUST_0207</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5339000225067139</v>
+        <v>0.310699999332428</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -916,11 +916,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CUST_0934</t>
+          <t>CUST_0528</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5273000001907349</v>
+        <v>0.3043999969959259</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -929,11 +929,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CUST_1141</t>
+          <t>CUST_0992</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5273000001907349</v>
+        <v>0.295199990272522</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -942,11 +942,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CUST_0992</t>
+          <t>CUST_0219</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5273000001907349</v>
+        <v>0.2635999917984009</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -955,11 +955,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CUST_0179</t>
+          <t>CUST_0038</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.524399995803833</v>
+        <v>0.2621999979019165</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -968,11 +968,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CUST_0666</t>
+          <t>CUST_0996</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.522599995136261</v>
+        <v>0.2612999975681305</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -981,11 +981,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CUST_0210</t>
+          <t>CUST_0411</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.522599995136261</v>
+        <v>0.2560999989509583</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -994,11 +994,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CUST_0910</t>
+          <t>CUST_0045</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.522599995136261</v>
+        <v>0.2535000145435333</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1007,11 +1007,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CUST_0007</t>
+          <t>CUST_0934</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5210999846458435</v>
+        <v>0.2406000047922134</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1020,11 +1020,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CUST_0548</t>
+          <t>CUST_0072</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5210999846458435</v>
+        <v>0.2388000041246414</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1033,11 +1033,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CUST_0095</t>
+          <t>CUST_1180</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.513700008392334</v>
+        <v>0.2343000024557114</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1046,11 +1046,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CUST_0477</t>
+          <t>CUST_0000</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.513700008392334</v>
+        <v>0.2234999984502792</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1059,11 +1059,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CUST_0465</t>
+          <t>CUST_0224</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.513700008392334</v>
+        <v>0.2119999974966049</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -1072,11 +1072,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CUST_0878</t>
+          <t>CUST_0682</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.513700008392334</v>
+        <v>0.2031999975442886</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1085,11 +1085,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CUST_0490</t>
+          <t>CUST_1070</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5120999813079834</v>
+        <v>0.2004999965429306</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -1098,11 +1098,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CUST_0261</t>
+          <t>CUST_0015</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5062000155448914</v>
+        <v>0.1997999995946884</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1111,11 +1111,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CUST_0155</t>
+          <t>CUST_1088</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5011000037193298</v>
+        <v>0.1976999938488007</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CUST_0691</t>
+          <t>CUST_0210</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5005999803543091</v>
+        <v>0.1968999952077866</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1137,11 +1137,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CUST_0159</t>
+          <t>CUST_0493</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5</v>
+        <v>0.1905999928712845</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1150,11 +1150,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CUST_0841</t>
+          <t>CUST_0086</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5</v>
+        <v>0.1869000047445297</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -1163,11 +1163,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CUST_0861</t>
+          <t>CUST_0490</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4995000064373016</v>
+        <v>0.1844999939203262</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1176,11 +1176,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CUST_1026</t>
+          <t>CUST_0138</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4981000125408173</v>
+        <v>0.1835000067949295</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1189,11 +1189,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CUST_0783</t>
+          <t>CUST_0730</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4970999956130981</v>
+        <v>0.177499994635582</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -1202,11 +1202,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CUST_0028</t>
+          <t>CUST_0599</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4941000044345856</v>
+        <v>0.1773999929428101</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -1215,11 +1215,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CUST_0345</t>
+          <t>CUST_0666</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.492900013923645</v>
+        <v>0.1738000065088272</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -1228,11 +1228,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CUST_0726</t>
+          <t>CUST_0571</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4918999969959259</v>
+        <v>0.1712000072002411</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -1241,11 +1241,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CUST_0208</t>
+          <t>CUST_1087</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4918000102043152</v>
+        <v>0.1710000038146973</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -1254,11 +1254,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CUST_0626</t>
+          <t>CUST_0455</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4909999966621399</v>
+        <v>0.1647000014781952</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -1267,11 +1267,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CUST_1193</t>
+          <t>CUST_0929</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4905000030994415</v>
+        <v>0.164000004529953</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -1280,11 +1280,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CUST_0224</t>
+          <t>CUST_0954</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4905000030994415</v>
+        <v>0.1621000021696091</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -1293,11 +1293,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CUST_1159</t>
+          <t>CUST_0925</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.488400012254715</v>
+        <v>0.161300003528595</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -1306,11 +1306,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CUST_1097</t>
+          <t>CUST_0425</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4869999885559082</v>
+        <v>0.1542000025510788</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -1319,11 +1319,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CUST_0166</t>
+          <t>CUST_0159</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4869999885559082</v>
+        <v>0.1527999937534332</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -1332,11 +1332,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CUST_0989</t>
+          <t>CUST_0218</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4869999885559082</v>
+        <v>0.1523000001907349</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -1345,11 +1345,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CUST_0429</t>
+          <t>CUST_0028</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4869999885559082</v>
+        <v>0.1512999981641769</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -1358,11 +1358,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CUST_0412</t>
+          <t>CUST_0119</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4824999868869781</v>
+        <v>0.1481000036001205</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -1371,11 +1371,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CUST_0119</t>
+          <t>CUST_0367</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4726999998092651</v>
+        <v>0.1477999985218048</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -1384,11 +1384,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CUST_0929</t>
+          <t>CUST_0310</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4726999998092651</v>
+        <v>0.1386000066995621</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1397,11 +1397,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CUST_0599</t>
+          <t>CUST_0626</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4726999998092651</v>
+        <v>0.1377000063657761</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -1410,11 +1410,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CUST_0086</t>
+          <t>CUST_0095</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4650999903678894</v>
+        <v>0.1281999945640564</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -1423,11 +1423,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CUST_0585</t>
+          <t>CUST_0630</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4641999900341034</v>
+        <v>0.125900000333786</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -1436,11 +1436,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CUST_0367</t>
+          <t>CUST_0881</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4638999998569489</v>
+        <v>0.1238999962806702</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -1449,11 +1449,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CUST_0547</t>
+          <t>CUST_0652</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4611999988555908</v>
+        <v>0.1229000017046928</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1462,11 +1462,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CUST_1070</t>
+          <t>CUST_0013</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.460099995136261</v>
+        <v>0.1216000020503998</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -1475,11 +1475,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CUST_0069</t>
+          <t>CUST_1122</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4593000113964081</v>
+        <v>0.1169999986886978</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -1488,11 +1488,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CUST_0600</t>
+          <t>CUST_0208</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4593000113964081</v>
+        <v>0.1125999987125397</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -1501,11 +1501,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CUST_0491</t>
+          <t>CUST_0867</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4560999870300293</v>
+        <v>0.1099999994039536</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1514,11 +1514,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CUST_0358</t>
+          <t>CUST_0007</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4560999870300293</v>
+        <v>0.1081999987363815</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -1527,11 +1527,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CUST_1111</t>
+          <t>CUST_0709</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4560999870300293</v>
+        <v>0.1049999967217445</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -1540,11 +1540,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CUST_0273</t>
+          <t>CUST_0337</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.454800009727478</v>
+        <v>0.1036000028252602</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CUST_0996</t>
+          <t>CUST_0848</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.454800009727478</v>
+        <v>0.100100003182888</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1566,11 +1566,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CUST_0881</t>
+          <t>CUST_0531</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09870000183582306</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -1579,11 +1579,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CUST_0794</t>
+          <t>CUST_0465</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09740000218153</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -1592,11 +1592,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CUST_0038</t>
+          <t>CUST_0857</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09650000184774399</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -1605,11 +1605,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CUST_1134</t>
+          <t>CUST_1163</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09239999949932098</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -1618,11 +1618,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CUST_0411</t>
+          <t>CUST_0507</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09160000085830688</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -1631,11 +1631,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CUST_0310</t>
+          <t>CUST_0517</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.454800009727478</v>
+        <v>0.0908999964594841</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -1644,11 +1644,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CUST_0538</t>
+          <t>CUST_0975</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.454800009727478</v>
+        <v>0.09040000289678574</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1657,11 +1657,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CUST_0502</t>
+          <t>CUST_1193</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.454800009727478</v>
+        <v>0.08309999853372574</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1670,11 +1670,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CUST_0493</t>
+          <t>CUST_0308</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.454800009727478</v>
+        <v>0.08030000329017639</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CUST_0015</t>
+          <t>CUST_0639</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.454800009727478</v>
+        <v>0.07989999651908875</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -1696,11 +1696,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CUST_0608</t>
+          <t>CUST_0726</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4533999860286713</v>
+        <v>0.07919999957084656</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -1709,11 +1709,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CUST_1087</t>
+          <t>CUST_0894</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4533999860286713</v>
+        <v>0.07890000194311142</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -1722,11 +1722,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CUST_0000</t>
+          <t>CUST_0783</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4533999860286713</v>
+        <v>0.07800000160932541</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -1735,11 +1735,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CUST_0981</t>
+          <t>CUST_1141</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4526000022888184</v>
+        <v>0.07769999653100967</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -1748,11 +1748,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CUST_0406</t>
+          <t>CUST_0393</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.450300008058548</v>
+        <v>0.07750000059604645</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -1761,11 +1761,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CUST_0072</t>
+          <t>CUST_1035</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4496999979019165</v>
+        <v>0.07649999856948853</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -1774,11 +1774,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CUST_0425</t>
+          <t>CUST_0459</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4478999972343445</v>
+        <v>0.07649999856948853</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -1787,11 +1787,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CUST_0442</t>
+          <t>CUST_0502</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4447000026702881</v>
+        <v>0.07649999856948853</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -1800,11 +1800,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CUST_1021</t>
+          <t>CUST_0585</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4361000061035156</v>
+        <v>0.07590000331401825</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -1813,11 +1813,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CUST_0933</t>
+          <t>CUST_0412</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4280999898910522</v>
+        <v>0.07320000231266022</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1826,11 +1826,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CUST_0163</t>
+          <t>CUST_0477</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4273999929428101</v>
+        <v>0.07190000265836716</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1839,11 +1839,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CUST_0925</t>
+          <t>CUST_0050</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4273999929428101</v>
+        <v>0.07050000131130219</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -1852,11 +1852,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CUST_0867</t>
+          <t>CUST_1159</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4259999990463257</v>
+        <v>0.06909999996423721</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -1865,11 +1865,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CUST_0255</t>
+          <t>CUST_0738</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4253999888896942</v>
+        <v>0.06669999659061432</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -1878,11 +1878,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CUST_0279</t>
+          <t>CUST_0616</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4239000082015991</v>
+        <v>0.06530000269412994</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1891,11 +1891,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CUST_0848</t>
+          <t>CUST_0124</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4223999977111816</v>
+        <v>0.06480000168085098</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -1904,11 +1904,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CUST_0571</t>
+          <t>CUST_0345</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06430000066757202</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -1917,11 +1917,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CUST_0068</t>
+          <t>CUST_0273</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06360000371932983</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1930,11 +1930,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CUST_0943</t>
+          <t>CUST_0608</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06319999694824219</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -1943,11 +1943,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CUST_0730</t>
+          <t>CUST_0163</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06230000033974648</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -1956,11 +1956,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CUST_0455</t>
+          <t>CUST_0989</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06199999898672104</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -1969,11 +1969,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CUST_1065</t>
+          <t>CUST_0910</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4217999875545502</v>
+        <v>0.06150000169873238</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -1982,11 +1982,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CUST_0709</t>
+          <t>CUST_0155</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4205999970436096</v>
+        <v>0.06109999865293503</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -1995,11 +1995,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CUST_0898</t>
+          <t>CUST_1033</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4205999970436096</v>
+        <v>0.06080000102519989</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -2008,11 +2008,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CUST_0450</t>
+          <t>CUST_0794</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4205999970436096</v>
+        <v>0.06080000102519989</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -2021,11 +2021,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CUST_0148</t>
+          <t>CUST_0547</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4205999970436096</v>
+        <v>0.05700000002980232</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -2034,11 +2034,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CUST_0531</t>
+          <t>CUST_0018</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4185000061988831</v>
+        <v>0.05590000003576279</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -2047,11 +2047,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CUST_0424</t>
+          <t>CUST_0614</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4174999892711639</v>
+        <v>0.05429999902844429</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -2060,11 +2060,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CUST_0309</t>
+          <t>CUST_0878</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4162999987602234</v>
+        <v>0.05249999836087227</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2073,11 +2073,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CUST_1075</t>
+          <t>CUST_0577</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4162999987602234</v>
+        <v>0.0494999997317791</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -2086,11 +2086,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CUST_1146</t>
+          <t>CUST_0904</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4156999886035919</v>
+        <v>0.04930000007152557</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -2099,11 +2099,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CUST_0988</t>
+          <t>CUST_0255</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04839999973773956</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -2112,11 +2112,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CUST_1019</t>
+          <t>CUST_0841</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04809999838471413</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -2125,11 +2125,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CUST_0468</t>
+          <t>CUST_0933</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04760000109672546</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -2138,11 +2138,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CUST_1054</t>
+          <t>CUST_0092</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04760000109672546</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -2151,11 +2151,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CUST_0108</t>
+          <t>CUST_0145</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04650000110268593</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -2164,11 +2164,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CUST_0785</t>
+          <t>CUST_0373</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04650000110268593</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -2177,11 +2177,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CUST_0500</t>
+          <t>CUST_0044</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.0463000014424324</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -2190,11 +2190,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CUST_1033</t>
+          <t>CUST_0166</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04560000076889992</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -2203,11 +2203,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CUST_1120</t>
+          <t>CUST_0943</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04540000110864639</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -2216,11 +2216,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CUST_0907</t>
+          <t>CUST_0107</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04509999975562096</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -2229,11 +2229,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CUST_1123</t>
+          <t>CUST_1092</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04500000178813934</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -2242,11 +2242,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CUST_0323</t>
+          <t>CUST_1130</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.0438000001013279</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -2255,11 +2255,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CUST_0915</t>
+          <t>CUST_0139</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04349999874830246</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -2268,11 +2268,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CUST_0311</t>
+          <t>CUST_0538</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04320000112056732</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -2281,11 +2281,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CUST_1131</t>
+          <t>CUST_0548</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.04289999976754189</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2294,11 +2294,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CUST_0291</t>
+          <t>CUST_0295</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4144000113010406</v>
+        <v>0.0421999990940094</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2307,11 +2307,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CUST_1073</t>
+          <t>CUST_1065</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4129000008106232</v>
+        <v>0.04089999943971634</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2320,11 +2320,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CUST_1035</t>
+          <t>CUST_1097</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4113999903202057</v>
+        <v>0.0390000008046627</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2333,11 +2333,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CUST_0868</t>
+          <t>CUST_1022</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.3955999910831451</v>
+        <v>0.03779999911785126</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2346,11 +2346,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CUST_0107</t>
+          <t>CUST_0760</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.3935000002384186</v>
+        <v>0.03579999879002571</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2359,11 +2359,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CUST_0393</t>
+          <t>CUST_1021</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.393200010061264</v>
+        <v>0.03339999914169312</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2372,11 +2372,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CUST_0630</t>
+          <t>CUST_0424</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.3928999900817871</v>
+        <v>0.03310000151395798</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2385,11 +2385,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CUST_0975</t>
+          <t>CUST_0866</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.03290000185370445</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2398,11 +2398,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CUST_1058</t>
+          <t>CUST_1067</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.03109999932348728</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2411,11 +2411,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CUST_0399</t>
+          <t>CUST_0489</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.03070000000298023</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2424,11 +2424,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CUST_0800</t>
+          <t>CUST_0069</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.03060000017285347</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2437,11 +2437,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CUST_0643</t>
+          <t>CUST_1101</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.03040000051259995</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2450,11 +2450,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CUST_1067</t>
+          <t>CUST_1123</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.3889000117778778</v>
+        <v>0.02999999932944775</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2463,11 +2463,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CUST_0222</t>
+          <t>CUST_0379</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.3878999948501587</v>
+        <v>0.02989999949932098</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2476,11 +2476,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CUST_0044</t>
+          <t>CUST_0296</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.387800008058548</v>
+        <v>0.02979999966919422</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2489,11 +2489,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CUST_1088</t>
+          <t>CUST_0429</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.387800008058548</v>
+        <v>0.02920000068843365</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2502,11 +2502,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CUST_1043</t>
+          <t>CUST_0704</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.3851999938488007</v>
+        <v>0.02869999967515469</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2515,11 +2515,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CUST_0741</t>
+          <t>CUST_0865</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3849000036716461</v>
+        <v>0.02850000001490116</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2528,11 +2528,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CUST_0139</t>
+          <t>CUST_0001</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.3849000036716461</v>
+        <v>0.02830000035464764</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -2541,11 +2541,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CUST_0092</t>
+          <t>CUST_0796</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.382999986410141</v>
+        <v>0.02800000086426735</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2554,11 +2554,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CUST_0914</t>
+          <t>CUST_0142</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.382999986410141</v>
+        <v>0.02630000002682209</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -2567,11 +2567,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CUST_0219</t>
+          <t>CUST_0750</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.382999986410141</v>
+        <v>0.02630000002682209</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2580,11 +2580,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CUST_0445</t>
+          <t>CUST_0877</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.382999986410141</v>
+        <v>0.02610000036656857</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -2593,11 +2593,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CUST_0082</t>
+          <t>CUST_0696</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.3828000128269196</v>
+        <v>0.02529999986290932</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -2606,11 +2606,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CUST_0838</t>
+          <t>CUST_1051</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02500000037252903</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2619,11 +2619,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CUST_0639</t>
+          <t>CUST_0274</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02490000054240227</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -2632,11 +2632,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CUST_0413</t>
+          <t>CUST_1064</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02490000054240227</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -2645,11 +2645,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CUST_0654</t>
+          <t>CUST_1195</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02470000088214874</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -2658,11 +2658,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CUST_0615</t>
+          <t>CUST_0082</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02459999918937683</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -2671,11 +2671,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CUST_0295</t>
+          <t>CUST_0622</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02459999918937683</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -2684,11 +2684,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CUST_0871</t>
+          <t>CUST_0600</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.3810999989509583</v>
+        <v>0.02390000037848949</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -2697,11 +2697,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CUST_0937</t>
+          <t>CUST_0443</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3801000118255615</v>
+        <v>0.02380000054836273</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -2710,11 +2710,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CUST_0427</t>
+          <t>CUST_0214</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.3801000118255615</v>
+        <v>0.02380000054836273</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -2723,11 +2723,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CUST_0346</t>
+          <t>CUST_0148</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.3801000118255615</v>
+        <v>0.02309999987483025</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -2736,11 +2736,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CUST_0719</t>
+          <t>CUST_0741</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.3801000118255615</v>
+        <v>0.02290000021457672</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -2749,11 +2749,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CUST_0614</t>
+          <t>CUST_1080</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02260000072419643</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2762,11 +2762,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CUST_0954</t>
+          <t>CUST_0275</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02260000072419643</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -2775,11 +2775,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CUST_0296</t>
+          <t>CUST_0735</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.022299999371171</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -2788,11 +2788,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CUST_0507</t>
+          <t>CUST_1107</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02199999988079071</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -2801,11 +2801,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CUST_0750</t>
+          <t>CUST_0244</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02180000022053719</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -2814,11 +2814,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CUST_0904</t>
+          <t>CUST_0004</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02170000039041042</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -2827,11 +2827,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CUST_0337</t>
+          <t>CUST_0450</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.3799000084400177</v>
+        <v>0.02160000056028366</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -2840,11 +2840,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CUST_0432</t>
+          <t>CUST_0722</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.3756000101566315</v>
+        <v>0.02119999937713146</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2853,11 +2853,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CUST_1098</t>
+          <t>CUST_0454</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.3756000101566315</v>
+        <v>0.02099999971687794</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -2866,11 +2866,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CUST_0738</t>
+          <t>CUST_0500</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02089999988675117</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -2879,11 +2879,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CUST_0042</t>
+          <t>CUST_0222</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02089999988675117</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -2892,11 +2892,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CUST_0616</t>
+          <t>CUST_0323</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02080000005662441</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -2905,11 +2905,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CUST_0065</t>
+          <t>CUST_0615</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02080000005662441</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2918,11 +2918,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CUST_0705</t>
+          <t>CUST_0423</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02070000022649765</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2931,11 +2931,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CUST_0040</t>
+          <t>CUST_0445</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02060000039637089</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -2944,11 +2944,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CUST_0361</t>
+          <t>CUST_0785</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02050000056624413</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2957,11 +2957,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CUST_0171</t>
+          <t>CUST_0660</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.0203000009059906</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -2970,11 +2970,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CUST_0695</t>
+          <t>CUST_0221</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02019999921321869</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -2983,11 +2983,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CUST_0050</t>
+          <t>CUST_0651</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.3535999953746796</v>
+        <v>0.02019999921321869</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -2996,11 +2996,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CUST_0759</t>
+          <t>CUST_0742</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.3531999886035919</v>
+        <v>0.01999999955296516</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -3009,11 +3009,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CUST_0075</t>
+          <t>CUST_0413</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.0198999997228384</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -3022,11 +3022,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CUST_0580</t>
+          <t>CUST_0183</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.0198999997228384</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -3035,11 +3035,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CUST_0070</t>
+          <t>CUST_0040</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.0198999997228384</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -3048,11 +3048,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CUST_0667</t>
+          <t>CUST_0376</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01970000006258488</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -3061,11 +3061,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CUST_0533</t>
+          <t>CUST_0774</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01960000023245811</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -3074,11 +3074,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CUST_0376</t>
+          <t>CUST_0448</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01940000057220459</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -3087,11 +3087,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CUST_0438</t>
+          <t>CUST_0194</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01920000091195107</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -3100,11 +3100,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CUST_0471</t>
+          <t>CUST_0111</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01920000091195107</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -3113,11 +3113,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CUST_0731</t>
+          <t>CUST_0200</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3526000082492828</v>
+        <v>0.01909999921917915</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -3126,11 +3126,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CUST_0147</t>
+          <t>CUST_1134</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3508000075817108</v>
+        <v>0.01899999938905239</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -3139,11 +3139,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CUST_0218</t>
+          <t>CUST_1090</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.3508000075817108</v>
+        <v>0.01860000006854534</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -3152,11 +3152,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CUST_0592</t>
+          <t>CUST_1040</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01850000023841858</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -3165,11 +3165,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CUST_0622</t>
+          <t>CUST_1098</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01840000040829182</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -3178,11 +3178,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CUST_0489</t>
+          <t>CUST_0220</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01840000040829182</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -3191,11 +3191,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CUST_0145</t>
+          <t>CUST_1072</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01830000057816505</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -3204,11 +3204,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CUST_0866</t>
+          <t>CUST_0636</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01820000074803829</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -3217,11 +3217,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CUST_1080</t>
+          <t>CUST_0346</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01820000074803829</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -3230,11 +3230,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CUST_0723</t>
+          <t>CUST_1110</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01779999956488609</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -3243,11 +3243,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CUST_1090</t>
+          <t>CUST_0064</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01769999973475933</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -3256,11 +3256,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CUST_1122</t>
+          <t>CUST_1121</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01769999973475933</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -3269,11 +3269,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CUST_0857</t>
+          <t>CUST_1073</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01750000007450581</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -3282,11 +3282,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CUST_0416</t>
+          <t>CUST_0555</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01740000024437904</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -3295,11 +3295,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CUST_1084</t>
+          <t>CUST_0533</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.350600004196167</v>
+        <v>0.01730000041425228</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -3308,11 +3308,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CUST_0869</t>
+          <t>CUST_0952</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.3504000008106232</v>
+        <v>0.01720000058412552</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -3321,11 +3321,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CUST_0379</t>
+          <t>CUST_1106</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.3504000008106232</v>
+        <v>0.01710000075399876</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -3334,11 +3334,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CUST_0647</t>
+          <t>CUST_1084</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.3504000008106232</v>
+        <v>0.01710000075399876</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -3347,11 +3347,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CUST_0652</t>
+          <t>CUST_0981</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.3501000106334686</v>
+        <v>0.01689999923110008</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -3360,11 +3360,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CUST_0244</t>
+          <t>CUST_0731</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.3501000106334686</v>
+        <v>0.01679999940097332</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -3373,11 +3373,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CUST_0214</t>
+          <t>CUST_1003</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.3501000106334686</v>
+        <v>0.01669999957084656</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -3386,11 +3386,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CUST_0735</t>
+          <t>CUST_0097</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.3501000106334686</v>
+        <v>0.0165999997407198</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -3399,11 +3399,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CUST_0790</t>
+          <t>CUST_0427</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.0165999997407198</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -3412,11 +3412,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CUST_0239</t>
+          <t>CUST_0401</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.0165999997407198</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -3425,11 +3425,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CUST_0821</t>
+          <t>CUST_0529</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.0165999997407198</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -3438,11 +3438,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CUST_1106</t>
+          <t>CUST_0664</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.01640000008046627</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -3451,11 +3451,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CUST_0496</t>
+          <t>CUST_0491</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.01610000059008598</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -3464,11 +3464,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CUST_1125</t>
+          <t>CUST_0907</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.3495999872684479</v>
+        <v>0.01610000059008598</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -3477,11 +3477,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CUST_0658</t>
+          <t>CUST_0811</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.3492000102996826</v>
+        <v>0.01600000075995922</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -3490,11 +3490,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CUST_0912</t>
+          <t>CUST_0580</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01600000075995922</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -3503,11 +3503,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CUST_0883</t>
+          <t>CUST_0108</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01590000092983246</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -3516,11 +3516,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CUST_0899</t>
+          <t>CUST_0898</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01559999957680702</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -3529,11 +3529,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CUST_0844</t>
+          <t>CUST_0532</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01549999974668026</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -3542,11 +3542,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CUST_0078</t>
+          <t>CUST_1043</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01549999974668026</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -3555,11 +3555,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CUST_0885</t>
+          <t>CUST_0388</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01549999974668026</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -3568,11 +3568,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CUST_0935</t>
+          <t>CUST_0723</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0153999999165535</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -3581,11 +3581,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CUST_0837</t>
+          <t>CUST_1058</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0153999999165535</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -3594,11 +3594,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CUST_0891</t>
+          <t>CUST_0643</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01530000008642673</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -3607,11 +3607,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CUST_0832</t>
+          <t>CUST_0915</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01530000008642673</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -3620,11 +3620,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CUST_0939</t>
+          <t>CUST_1184</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01510000042617321</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -3633,11 +3633,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CUST_0826</t>
+          <t>CUST_0193</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01510000042617321</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -3646,11 +3646,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CUST_0940</t>
+          <t>CUST_0743</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01499999966472387</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -3659,11 +3659,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CUST_0853</t>
+          <t>CUST_0498</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01489999983459711</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -3672,11 +3672,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CUST_0854</t>
+          <t>CUST_0291</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01480000000447035</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -3685,11 +3685,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CUST_0918</t>
+          <t>CUST_0453</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01480000000447035</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -3698,11 +3698,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CUST_0074</t>
+          <t>CUST_0276</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01480000000447035</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -3711,11 +3711,11 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CUST_0879</t>
+          <t>CUST_0042</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01480000000447035</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -3724,11 +3724,11 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CUST_0901</t>
+          <t>CUST_1125</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01439999975264072</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -3737,11 +3737,11 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CUST_0906</t>
+          <t>CUST_0891</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01429999992251396</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -3750,11 +3750,11 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CUST_0859</t>
+          <t>CUST_0758</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0142000000923872</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -3763,11 +3763,11 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CUST_0076</t>
+          <t>CUST_0406</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01389999967068434</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -3776,11 +3776,11 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CUST_0863</t>
+          <t>CUST_1178</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01379999984055758</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -3789,11 +3789,11 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CUST_0865</t>
+          <t>CUST_0998</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01370000001043081</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -3802,11 +3802,11 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CUST_0932</t>
+          <t>CUST_0468</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01370000001043081</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -3815,11 +3815,11 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CUST_0892</t>
+          <t>CUST_0763</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01370000001043081</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -3828,11 +3828,11 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CUST_0873</t>
+          <t>CUST_0318</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01360000018030405</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -3841,11 +3841,11 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CUST_0071</t>
+          <t>CUST_0309</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01360000018030405</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -3854,11 +3854,11 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CUST_0923</t>
+          <t>CUST_1120</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01360000018030405</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -3867,11 +3867,11 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CUST_0877</t>
+          <t>CUST_0800</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01350000035017729</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -3880,11 +3880,11 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CUST_0205</t>
+          <t>CUST_0471</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01350000035017729</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -3893,11 +3893,11 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CUST_0945</t>
+          <t>CUST_0250</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01339999958872795</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -3906,11 +3906,11 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CUST_1154</t>
+          <t>CUST_0070</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01319999992847443</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -3919,11 +3919,11 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CUST_1152</t>
+          <t>CUST_0361</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01310000009834766</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -3932,11 +3932,11 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CUST_1144</t>
+          <t>CUST_0442</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0130000002682209</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -3945,11 +3945,11 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CUST_0021</t>
+          <t>CUST_0695</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01290000043809414</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -3958,11 +3958,11 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CUST_0026</t>
+          <t>CUST_0239</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01290000043809414</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -3971,11 +3971,11 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CUST_1132</t>
+          <t>CUST_0399</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01290000043809414</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -3984,11 +3984,11 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CUST_1130</t>
+          <t>CUST_0075</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0127999996766448</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -3997,11 +3997,11 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CUST_1128</t>
+          <t>CUST_0311</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0127999996766448</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -4010,11 +4010,11 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CUST_1121</t>
+          <t>CUST_0518</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01269999984651804</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -4023,11 +4023,11 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CUST_1115</t>
+          <t>CUST_0667</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01269999984651804</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -4036,11 +4036,11 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CUST_1114</t>
+          <t>CUST_1111</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01260000001639128</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -4049,11 +4049,11 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CUST_0037</t>
+          <t>CUST_0871</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01250000018626451</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -4062,11 +4062,11 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CUST_1110</t>
+          <t>CUST_0759</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01240000035613775</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -4075,11 +4075,11 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CUST_1107</t>
+          <t>CUST_1156</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01229999959468842</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -4088,11 +4088,11 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CUST_1103</t>
+          <t>CUST_1049</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01229999959468842</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -4101,11 +4101,11 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CUST_1101</t>
+          <t>CUST_0705</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01190000027418137</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -4114,11 +4114,11 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CUST_1153</t>
+          <t>CUST_0970</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0118000004440546</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -4127,11 +4127,11 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CUST_1155</t>
+          <t>CUST_0780</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0118000004440546</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -4140,11 +4140,11 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CUST_1099</t>
+          <t>CUST_0997</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01169999968260527</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -4153,11 +4153,11 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CUST_1156</t>
+          <t>CUST_0937</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0115999998524785</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -4166,11 +4166,11 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CUST_1195</t>
+          <t>CUST_0592</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0115999998524785</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -4179,11 +4179,11 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CUST_0004</t>
+          <t>CUST_0526</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01150000002235174</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -4192,11 +4192,11 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CUST_0008</t>
+          <t>CUST_0734</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01140000019222498</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -4205,11 +4205,11 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CUST_1184</t>
+          <t>CUST_0826</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01140000019222498</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -4218,11 +4218,11 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CUST_1183</t>
+          <t>CUST_0863</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01140000019222498</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -4231,11 +4231,11 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CUST_1182</t>
+          <t>CUST_0432</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01119999960064888</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
@@ -4244,11 +4244,11 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CUST_1181</t>
+          <t>CUST_0098</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01119999960064888</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -4257,11 +4257,11 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CUST_0009</t>
+          <t>CUST_0745</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01080000028014183</v>
       </c>
       <c r="C295" t="n">
         <v>0</v>
@@ -4270,11 +4270,11 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CUST_1179</t>
+          <t>CUST_0912</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01080000028014183</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -4283,11 +4283,11 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CUST_1178</t>
+          <t>CUST_0654</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01080000028014183</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -4296,11 +4296,11 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CUST_1176</t>
+          <t>CUST_0046</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01070000045001507</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -4309,11 +4309,11 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CUST_0010</t>
+          <t>CUST_0438</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01070000045001507</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -4322,11 +4322,11 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CUST_1164</t>
+          <t>CUST_0627</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01049999985843897</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -4335,11 +4335,11 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CUST_1163</t>
+          <t>CUST_0658</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01040000002831221</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -4348,11 +4348,11 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CUST_0017</t>
+          <t>CUST_0204</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01040000002831221</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -4361,11 +4361,11 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CUST_1100</t>
+          <t>CUST_0083</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01020000036805868</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -4374,11 +4374,11 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>CUST_1092</t>
+          <t>CUST_0071</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01020000036805868</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -4387,11 +4387,11 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CUST_0066</t>
+          <t>CUST_0205</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.01020000036805868</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -4400,11 +4400,11 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CUST_0059</t>
+          <t>CUST_0816</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009999999776482582</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -4413,11 +4413,11 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CUST_1003</t>
+          <t>CUST_0812</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009999999776482582</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -4426,11 +4426,11 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CUST_0999</t>
+          <t>CUST_1005</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00989999994635582</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -4439,11 +4439,11 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CUST_0998</t>
+          <t>CUST_1099</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00989999994635582</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -4452,11 +4452,11 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CUST_0997</t>
+          <t>CUST_0271</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009800000116229057</v>
       </c>
       <c r="C310" t="n">
         <v>0</v>
@@ -4465,11 +4465,11 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CUST_0061</t>
+          <t>CUST_0385</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009700000286102295</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -4478,11 +4478,11 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CUST_0995</t>
+          <t>CUST_1114</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009700000286102295</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -4491,11 +4491,11 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CUST_0993</t>
+          <t>CUST_0017</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009600000455975533</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -4504,11 +4504,11 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CUST_0062</t>
+          <t>CUST_0416</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009600000455975533</v>
       </c>
       <c r="C314" t="n">
         <v>0</v>
@@ -4517,11 +4517,11 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CUST_0064</t>
+          <t>CUST_1146</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009600000455975533</v>
       </c>
       <c r="C315" t="n">
         <v>0</v>
@@ -4530,11 +4530,11 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CUST_0984</t>
+          <t>CUST_0790</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009499999694526196</v>
       </c>
       <c r="C316" t="n">
         <v>0</v>
@@ -4543,11 +4543,11 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CUST_0980</t>
+          <t>CUST_0677</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009399999864399433</v>
       </c>
       <c r="C317" t="n">
         <v>0</v>
@@ -4556,11 +4556,11 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CUST_0972</t>
+          <t>CUST_0619</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009300000034272671</v>
       </c>
       <c r="C318" t="n">
         <v>0</v>
@@ -4569,11 +4569,11 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CUST_0970</t>
+          <t>CUST_1198</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009300000034272671</v>
       </c>
       <c r="C319" t="n">
         <v>0</v>
@@ -4582,11 +4582,11 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CUST_0960</t>
+          <t>CUST_0680</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.009200000204145908</v>
       </c>
       <c r="C320" t="n">
         <v>0</v>
@@ -4595,11 +4595,11 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CUST_0952</t>
+          <t>CUST_0421</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008999999612569809</v>
       </c>
       <c r="C321" t="n">
         <v>0</v>
@@ -4608,11 +4608,11 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CUST_1005</t>
+          <t>CUST_0542</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008999999612569809</v>
       </c>
       <c r="C322" t="n">
         <v>0</v>
@@ -4621,11 +4621,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CUST_1009</t>
+          <t>CUST_0679</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008999999612569809</v>
       </c>
       <c r="C323" t="n">
         <v>0</v>
@@ -4634,11 +4634,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CUST_1083</t>
+          <t>CUST_0358</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008999999612569809</v>
       </c>
       <c r="C324" t="n">
         <v>0</v>
@@ -4647,11 +4647,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CUST_1015</t>
+          <t>CUST_0634</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008899999782443047</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -4660,11 +4660,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CUST_1072</t>
+          <t>CUST_0567</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008700000122189522</v>
       </c>
       <c r="C326" t="n">
         <v>0</v>
@@ -4673,11 +4673,11 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CUST_1071</t>
+          <t>CUST_0993</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008700000122189522</v>
       </c>
       <c r="C327" t="n">
         <v>0</v>
@@ -4686,11 +4686,11 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CUST_0046</t>
+          <t>CUST_1075</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008600000292062759</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -4699,11 +4699,11 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CUST_1064</t>
+          <t>CUST_0161</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008500000461935997</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -4712,11 +4712,11 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>CUST_1056</t>
+          <t>CUST_1036</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008500000461935997</v>
       </c>
       <c r="C330" t="n">
         <v>0</v>
@@ -4725,11 +4725,11 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CUST_1051</t>
+          <t>CUST_0420</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008500000461935997</v>
       </c>
       <c r="C331" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CUST_1049</t>
+          <t>CUST_0572</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008500000461935997</v>
       </c>
       <c r="C332" t="n">
         <v>0</v>
@@ -4751,11 +4751,11 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CUST_1048</t>
+          <t>CUST_0879</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008299999870359898</v>
       </c>
       <c r="C333" t="n">
         <v>0</v>
@@ -4764,11 +4764,11 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CUST_1040</t>
+          <t>CUST_0689</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008299999870359898</v>
       </c>
       <c r="C334" t="n">
         <v>0</v>
@@ -4777,11 +4777,11 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CUST_1036</t>
+          <t>CUST_0838</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008299999870359898</v>
       </c>
       <c r="C335" t="n">
         <v>0</v>
@@ -4790,11 +4790,11 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CUST_1034</t>
+          <t>CUST_1131</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008299999870359898</v>
       </c>
       <c r="C336" t="n">
         <v>0</v>
@@ -4803,11 +4803,11 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CUST_0825</t>
+          <t>CUST_1024</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008299999870359898</v>
       </c>
       <c r="C337" t="n">
         <v>0</v>
@@ -4816,11 +4816,11 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CUST_0058</t>
+          <t>CUST_0059</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008200000040233135</v>
       </c>
       <c r="C338" t="n">
         <v>0</v>
@@ -4829,11 +4829,11 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CUST_1024</t>
+          <t>CUST_0591</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008200000040233135</v>
       </c>
       <c r="C339" t="n">
         <v>0</v>
@@ -4842,11 +4842,11 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CUST_1022</t>
+          <t>CUST_0280</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008200000040233135</v>
       </c>
       <c r="C340" t="n">
         <v>0</v>
@@ -4855,11 +4855,11 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CUST_1027</t>
+          <t>CUST_0649</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008200000040233135</v>
       </c>
       <c r="C341" t="n">
         <v>0</v>
@@ -4868,11 +4868,11 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>CUST_0088</t>
+          <t>CUST_0753</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008100000210106373</v>
       </c>
       <c r="C342" t="n">
         <v>0</v>
@@ -4881,11 +4881,11 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CUST_0823</t>
+          <t>CUST_0883</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008100000210106373</v>
       </c>
       <c r="C343" t="n">
         <v>0</v>
@@ -4894,11 +4894,11 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CUST_0421</t>
+          <t>CUST_0972</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.008100000210106373</v>
       </c>
       <c r="C344" t="n">
         <v>0</v>
@@ -4907,11 +4907,11 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CUST_0149</t>
+          <t>CUST_0140</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00800000037997961</v>
       </c>
       <c r="C345" t="n">
         <v>0</v>
@@ -4920,11 +4920,11 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CUST_0153</t>
+          <t>CUST_0770</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007899999618530273</v>
       </c>
       <c r="C346" t="n">
         <v>0</v>
@@ -4933,11 +4933,11 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CUST_0437</t>
+          <t>CUST_0844</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007899999618530273</v>
       </c>
       <c r="C347" t="n">
         <v>0</v>
@@ -4946,11 +4946,11 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CUST_0434</t>
+          <t>CUST_0715</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007899999618530273</v>
       </c>
       <c r="C348" t="n">
         <v>0</v>
@@ -4959,11 +4959,11 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CUST_0154</t>
+          <t>CUST_0508</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007799999788403511</v>
       </c>
       <c r="C349" t="n">
         <v>0</v>
@@ -4972,11 +4972,11 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CUST_0428</t>
+          <t>CUST_0486</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007699999958276749</v>
       </c>
       <c r="C350" t="n">
         <v>0</v>
@@ -4985,11 +4985,11 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CUST_0423</t>
+          <t>CUST_0932</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007499999832361937</v>
       </c>
       <c r="C351" t="n">
         <v>0</v>
@@ -4998,11 +4998,11 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CUST_0420</t>
+          <t>CUST_0081</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007499999832361937</v>
       </c>
       <c r="C352" t="n">
         <v>0</v>
@@ -5011,11 +5011,11 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CUST_0448</t>
+          <t>CUST_0068</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007400000002235174</v>
       </c>
       <c r="C353" t="n">
         <v>0</v>
@@ -5024,11 +5024,11 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CUST_0161</t>
+          <t>CUST_0814</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007400000002235174</v>
       </c>
       <c r="C354" t="n">
         <v>0</v>
@@ -5037,11 +5037,11 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CUST_0403</t>
+          <t>CUST_0869</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007300000172108412</v>
       </c>
       <c r="C355" t="n">
         <v>0</v>
@@ -5050,11 +5050,11 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CUST_0401</t>
+          <t>CUST_0764</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007300000172108412</v>
       </c>
       <c r="C356" t="n">
         <v>0</v>
@@ -5063,11 +5063,11 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CUST_0388</t>
+          <t>CUST_0859</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007199999876320362</v>
       </c>
       <c r="C357" t="n">
         <v>0</v>
@@ -5076,11 +5076,11 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CUST_0385</t>
+          <t>CUST_0248</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007199999876320362</v>
       </c>
       <c r="C358" t="n">
         <v>0</v>
@@ -5089,11 +5089,11 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CUST_0383</t>
+          <t>CUST_0823</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007199999876320362</v>
       </c>
       <c r="C359" t="n">
         <v>0</v>
@@ -5102,11 +5102,11 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CUST_0381</t>
+          <t>CUST_1103</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0071000000461936</v>
       </c>
       <c r="C360" t="n">
         <v>0</v>
@@ -5115,11 +5115,11 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CUST_0443</t>
+          <t>CUST_1132</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0071000000461936</v>
       </c>
       <c r="C361" t="n">
         <v>0</v>
@@ -5128,11 +5128,11 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CUST_0453</t>
+          <t>CUST_0170</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.0071000000461936</v>
       </c>
       <c r="C362" t="n">
         <v>0</v>
@@ -5141,11 +5141,11 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CUST_0373</t>
+          <t>CUST_0177</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007000000216066837</v>
       </c>
       <c r="C363" t="n">
         <v>0</v>
@@ -5154,11 +5154,11 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CUST_0140</t>
+          <t>CUST_0360</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.007000000216066837</v>
       </c>
       <c r="C364" t="n">
         <v>0</v>
@@ -5167,11 +5167,11 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CUST_0517</t>
+          <t>CUST_0621</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006800000090152025</v>
       </c>
       <c r="C365" t="n">
         <v>0</v>
@@ -5180,11 +5180,11 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CUST_0515</t>
+          <t>CUST_0428</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006800000090152025</v>
       </c>
       <c r="C366" t="n">
         <v>0</v>
@@ -5193,11 +5193,11 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CUST_0509</t>
+          <t>CUST_0549</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006800000090152025</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
@@ -5206,11 +5206,11 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CUST_0508</t>
+          <t>CUST_0484</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C368" t="n">
         <v>0</v>
@@ -5219,11 +5219,11 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CUST_0134</t>
+          <t>CUST_0363</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C369" t="n">
         <v>0</v>
@@ -5232,11 +5232,11 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CUST_0499</t>
+          <t>CUST_1176</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C370" t="n">
         <v>0</v>
@@ -5245,11 +5245,11 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CUST_0498</t>
+          <t>CUST_0058</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C371" t="n">
         <v>0</v>
@@ -5258,11 +5258,11 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CUST_0142</t>
+          <t>CUST_0074</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C372" t="n">
         <v>0</v>
@@ -5271,11 +5271,11 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CUST_0454</t>
+          <t>CUST_0171</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006699999794363976</v>
       </c>
       <c r="C373" t="n">
         <v>0</v>
@@ -5284,11 +5284,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CUST_0143</t>
+          <t>CUST_0354</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006599999964237213</v>
       </c>
       <c r="C374" t="n">
         <v>0</v>
@@ -5297,11 +5297,11 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CUST_0488</t>
+          <t>CUST_0134</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006599999964237213</v>
       </c>
       <c r="C375" t="n">
         <v>0</v>
@@ -5310,11 +5310,11 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CUST_0486</t>
+          <t>CUST_0381</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006500000134110451</v>
       </c>
       <c r="C376" t="n">
         <v>0</v>
@@ -5323,11 +5323,11 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CUST_0484</t>
+          <t>CUST_1181</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006500000134110451</v>
       </c>
       <c r="C377" t="n">
         <v>0</v>
@@ -5336,11 +5336,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CUST_0470</t>
+          <t>CUST_0008</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006500000134110451</v>
       </c>
       <c r="C378" t="n">
         <v>0</v>
@@ -5349,11 +5349,11 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CUST_0460</t>
+          <t>CUST_1144</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006500000134110451</v>
       </c>
       <c r="C379" t="n">
         <v>0</v>
@@ -5362,11 +5362,11 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CUST_0459</t>
+          <t>CUST_1054</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006399999838322401</v>
       </c>
       <c r="C380" t="n">
         <v>0</v>
@@ -5375,11 +5375,11 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CUST_0378</t>
+          <t>CUST_1083</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006399999838322401</v>
       </c>
       <c r="C381" t="n">
         <v>0</v>
@@ -5388,11 +5388,11 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CUST_0372</t>
+          <t>CUST_0656</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006300000008195639</v>
       </c>
       <c r="C382" t="n">
         <v>0</v>
@@ -5401,11 +5401,11 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CUST_0526</t>
+          <t>CUST_0061</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006300000008195639</v>
       </c>
       <c r="C383" t="n">
         <v>0</v>
@@ -5414,11 +5414,11 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CUST_0248</t>
+          <t>CUST_0901</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006300000008195639</v>
       </c>
       <c r="C384" t="n">
         <v>0</v>
@@ -5427,11 +5427,11 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CUST_0193</t>
+          <t>CUST_0331</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006300000008195639</v>
       </c>
       <c r="C385" t="n">
         <v>0</v>
@@ -5440,11 +5440,11 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CUST_0271</t>
+          <t>CUST_0515</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006099999882280827</v>
       </c>
       <c r="C386" t="n">
         <v>0</v>
@@ -5453,11 +5453,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CUST_0194</t>
+          <t>CUST_0403</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006099999882280827</v>
       </c>
       <c r="C387" t="n">
         <v>0</v>
@@ -5466,11 +5466,11 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CUST_0262</t>
+          <t>CUST_0470</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.006099999882280827</v>
       </c>
       <c r="C388" t="n">
         <v>0</v>
@@ -5479,11 +5479,11 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CUST_0195</t>
+          <t>CUST_0984</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005799999926239252</v>
       </c>
       <c r="C389" t="n">
         <v>0</v>
@@ -5492,11 +5492,11 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CUST_0259</t>
+          <t>CUST_0037</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005799999926239252</v>
       </c>
       <c r="C390" t="n">
         <v>0</v>
@@ -5505,11 +5505,11 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CUST_0250</t>
+          <t>CUST_0143</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005799999926239252</v>
       </c>
       <c r="C391" t="n">
         <v>0</v>
@@ -5518,11 +5518,11 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CUST_0242</t>
+          <t>CUST_0593</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005799999926239252</v>
       </c>
       <c r="C392" t="n">
         <v>0</v>
@@ -5531,11 +5531,11 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CUST_0275</t>
+          <t>CUST_0729</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00570000009611249</v>
       </c>
       <c r="C393" t="n">
         <v>0</v>
@@ -5544,11 +5544,11 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CUST_0199</t>
+          <t>CUST_0940</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00570000009611249</v>
       </c>
       <c r="C394" t="n">
         <v>0</v>
@@ -5557,11 +5557,11 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CUST_0200</t>
+          <t>CUST_1015</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00559999980032444</v>
       </c>
       <c r="C395" t="n">
         <v>0</v>
@@ -5570,11 +5570,11 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CUST_0234</t>
+          <t>CUST_0939</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00559999980032444</v>
       </c>
       <c r="C396" t="n">
         <v>0</v>
@@ -5583,11 +5583,11 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CUST_0231</t>
+          <t>CUST_0437</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00559999980032444</v>
       </c>
       <c r="C397" t="n">
         <v>0</v>
@@ -5596,11 +5596,11 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CUST_0204</t>
+          <t>CUST_0675</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00559999980032444</v>
       </c>
       <c r="C398" t="n">
         <v>0</v>
@@ -5609,11 +5609,11 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CUST_0221</t>
+          <t>CUST_0460</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C399" t="n">
         <v>0</v>
@@ -5622,11 +5622,11 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CUST_0220</t>
+          <t>CUST_0499</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C400" t="n">
         <v>0</v>
@@ -5635,11 +5635,11 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CUST_0274</t>
+          <t>CUST_1019</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C401" t="n">
         <v>0</v>
@@ -5648,11 +5648,11 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CUST_0276</t>
+          <t>CUST_0315</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C402" t="n">
         <v>0</v>
@@ -5661,11 +5661,11 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CUST_0170</t>
+          <t>CUST_0988</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C403" t="n">
         <v>0</v>
@@ -5674,11 +5674,11 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CUST_0331</t>
+          <t>CUST_0918</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C404" t="n">
         <v>0</v>
@@ -5687,11 +5687,11 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CUST_0363</t>
+          <t>CUST_0087</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C405" t="n">
         <v>0</v>
@@ -5700,11 +5700,11 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CUST_0360</t>
+          <t>CUST_0557</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C406" t="n">
         <v>0</v>
@@ -5713,11 +5713,11 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CUST_0359</t>
+          <t>CUST_0543</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005499999970197678</v>
       </c>
       <c r="C407" t="n">
         <v>0</v>
@@ -5726,11 +5726,11 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CUST_0355</t>
+          <t>CUST_0610</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C408" t="n">
         <v>0</v>
@@ -5739,11 +5739,11 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>CUST_0354</t>
+          <t>CUST_1100</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C409" t="n">
         <v>0</v>
@@ -5752,11 +5752,11 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CUST_0353</t>
+          <t>CUST_0892</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C410" t="n">
         <v>0</v>
@@ -5765,11 +5765,11 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CUST_0177</t>
+          <t>CUST_1115</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C411" t="n">
         <v>0</v>
@@ -5778,11 +5778,11 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CUST_0318</t>
+          <t>CUST_0558</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C412" t="n">
         <v>0</v>
@@ -5791,11 +5791,11 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CUST_0280</t>
+          <t>CUST_0719</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005400000140070915</v>
       </c>
       <c r="C413" t="n">
         <v>0</v>
@@ -5804,11 +5804,11 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CUST_0316</t>
+          <t>CUST_0076</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005299999844282866</v>
       </c>
       <c r="C414" t="n">
         <v>0</v>
@@ -5817,11 +5817,11 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CUST_0315</t>
+          <t>CUST_0021</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005299999844282866</v>
       </c>
       <c r="C415" t="n">
         <v>0</v>
@@ -5830,11 +5830,11 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CUST_0183</t>
+          <t>CUST_0009</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005299999844282866</v>
       </c>
       <c r="C416" t="n">
         <v>0</v>
@@ -5843,11 +5843,11 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CUST_0308</t>
+          <t>CUST_1152</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005299999844282866</v>
       </c>
       <c r="C417" t="n">
         <v>0</v>
@@ -5856,11 +5856,11 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CUST_0303</t>
+          <t>CUST_0147</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005299999844282866</v>
       </c>
       <c r="C418" t="n">
         <v>0</v>
@@ -5869,11 +5869,11 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CUST_0289</t>
+          <t>CUST_1027</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005200000014156103</v>
       </c>
       <c r="C419" t="n">
         <v>0</v>
@@ -5882,11 +5882,11 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CUST_0283</t>
+          <t>CUST_0595</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005200000014156103</v>
       </c>
       <c r="C420" t="n">
         <v>0</v>
@@ -5895,11 +5895,11 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CUST_0518</t>
+          <t>CUST_0149</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005100000184029341</v>
       </c>
       <c r="C421" t="n">
         <v>0</v>
@@ -5908,11 +5908,11 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CUST_0133</t>
+          <t>CUST_0065</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005100000184029341</v>
       </c>
       <c r="C422" t="n">
         <v>0</v>
@@ -5921,11 +5921,11 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CUST_0817</t>
+          <t>CUST_0262</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.005100000184029341</v>
       </c>
       <c r="C423" t="n">
         <v>0</v>
@@ -5934,11 +5934,11 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CUST_0722</t>
+          <t>CUST_1048</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C424" t="n">
         <v>0</v>
@@ -5947,11 +5947,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CUST_0753</t>
+          <t>CUST_0560</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C425" t="n">
         <v>0</v>
@@ -5960,11 +5960,11 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CUST_0745</t>
+          <t>CUST_0755</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C426" t="n">
         <v>0</v>
@@ -5973,11 +5973,11 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CUST_0743</t>
+          <t>CUST_0684</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C427" t="n">
         <v>0</v>
@@ -5986,11 +5986,11 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CUST_0742</t>
+          <t>CUST_0789</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C428" t="n">
         <v>0</v>
@@ -5999,11 +5999,11 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CUST_0734</t>
+          <t>CUST_0195</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C429" t="n">
         <v>0</v>
@@ -6012,11 +6012,11 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>CUST_0729</t>
+          <t>CUST_0825</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C430" t="n">
         <v>0</v>
@@ -6025,11 +6025,11 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CUST_0727</t>
+          <t>CUST_0496</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004999999888241291</v>
       </c>
       <c r="C431" t="n">
         <v>0</v>
@@ -6038,11 +6038,11 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CUST_0715</t>
+          <t>CUST_0980</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004900000058114529</v>
       </c>
       <c r="C432" t="n">
         <v>0</v>
@@ -6051,11 +6051,11 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CUST_0755</t>
+          <t>CUST_1056</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004900000058114529</v>
       </c>
       <c r="C433" t="n">
         <v>0</v>
@@ -6064,11 +6064,11 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CUST_0704</t>
+          <t>CUST_0372</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C434" t="n">
         <v>0</v>
@@ -6077,11 +6077,11 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CUST_0697</t>
+          <t>CUST_0817</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C435" t="n">
         <v>0</v>
@@ -6090,11 +6090,11 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CUST_0696</t>
+          <t>CUST_0242</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C436" t="n">
         <v>0</v>
@@ -6103,11 +6103,11 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CUST_0096</t>
+          <t>CUST_0383</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C437" t="n">
         <v>0</v>
@@ -6116,11 +6116,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CUST_0689</t>
+          <t>CUST_0231</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C438" t="n">
         <v>0</v>
@@ -6129,11 +6129,11 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CUST_0685</t>
+          <t>CUST_0378</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C439" t="n">
         <v>0</v>
@@ -6142,11 +6142,11 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CUST_0684</t>
+          <t>CUST_1155</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C440" t="n">
         <v>0</v>
@@ -6155,11 +6155,11 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CUST_0087</t>
+          <t>CUST_0118</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004800000227987766</v>
       </c>
       <c r="C441" t="n">
         <v>0</v>
@@ -6168,11 +6168,11 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CUST_0758</t>
+          <t>CUST_0353</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C442" t="n">
         <v>0</v>
@@ -6181,11 +6181,11 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CUST_0680</t>
+          <t>CUST_1153</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C443" t="n">
         <v>0</v>
@@ -6194,11 +6194,11 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CUST_0081</t>
+          <t>CUST_0133</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C444" t="n">
         <v>0</v>
@@ -6207,11 +6207,11 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CUST_0816</t>
+          <t>CUST_0509</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C445" t="n">
         <v>0</v>
@@ -6220,11 +6220,11 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CUST_0815</t>
+          <t>CUST_0821</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C446" t="n">
         <v>0</v>
@@ -6233,11 +6233,11 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CUST_0814</t>
+          <t>CUST_0853</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004600000102072954</v>
       </c>
       <c r="C447" t="n">
         <v>0</v>
@@ -6246,11 +6246,11 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CUST_0812</t>
+          <t>CUST_0781</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C448" t="n">
         <v>0</v>
@@ -6259,11 +6259,11 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CUST_0811</t>
+          <t>CUST_1183</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C449" t="n">
         <v>0</v>
@@ -6272,11 +6272,11 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CUST_0807</t>
+          <t>CUST_0885</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C450" t="n">
         <v>0</v>
@@ -6285,11 +6285,11 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CUST_0796</t>
+          <t>CUST_1164</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C451" t="n">
         <v>0</v>
@@ -6298,11 +6298,11 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CUST_0789</t>
+          <t>CUST_0854</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C452" t="n">
         <v>0</v>
@@ -6311,11 +6311,11 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CUST_0760</t>
+          <t>CUST_0199</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C453" t="n">
         <v>0</v>
@@ -6324,11 +6324,11 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CUST_0083</t>
+          <t>CUST_0289</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C454" t="n">
         <v>0</v>
@@ -6337,11 +6337,11 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CUST_0781</t>
+          <t>CUST_0303</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004499999806284904</v>
       </c>
       <c r="C455" t="n">
         <v>0</v>
@@ -6350,11 +6350,11 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>CUST_0780</t>
+          <t>CUST_0153</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004399999976158142</v>
       </c>
       <c r="C456" t="n">
         <v>0</v>
@@ -6363,11 +6363,11 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CUST_0774</t>
+          <t>CUST_1034</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004399999976158142</v>
       </c>
       <c r="C457" t="n">
         <v>0</v>
@@ -6376,11 +6376,11 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>CUST_0770</t>
+          <t>CUST_0129</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00430000014603138</v>
       </c>
       <c r="C458" t="n">
         <v>0</v>
@@ -6389,11 +6389,11 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CUST_0764</t>
+          <t>CUST_0837</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00430000014603138</v>
       </c>
       <c r="C459" t="n">
         <v>0</v>
@@ -6402,11 +6402,11 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CUST_0763</t>
+          <t>CUST_0088</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00430000014603138</v>
       </c>
       <c r="C460" t="n">
         <v>0</v>
@@ -6415,11 +6415,11 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CUST_0097</t>
+          <t>CUST_0642</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00430000014603138</v>
       </c>
       <c r="C461" t="n">
         <v>0</v>
@@ -6428,11 +6428,11 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CUST_0679</t>
+          <t>CUST_0960</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00419999985024333</v>
       </c>
       <c r="C462" t="n">
         <v>0</v>
@@ -6441,11 +6441,11 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CUST_0529</t>
+          <t>CUST_0923</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00419999985024333</v>
       </c>
       <c r="C463" t="n">
         <v>0</v>
@@ -6454,11 +6454,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CUST_0557</t>
+          <t>CUST_1179</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00419999985024333</v>
       </c>
       <c r="C464" t="n">
         <v>0</v>
@@ -6467,11 +6467,11 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CUST_0591</t>
+          <t>CUST_0832</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.00419999985024333</v>
       </c>
       <c r="C465" t="n">
         <v>0</v>
@@ -6480,11 +6480,11 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CUST_0118</t>
+          <t>CUST_0945</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004100000020116568</v>
       </c>
       <c r="C466" t="n">
         <v>0</v>
@@ -6493,11 +6493,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CUST_0577</t>
+          <t>CUST_0999</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004100000020116568</v>
       </c>
       <c r="C467" t="n">
         <v>0</v>
@@ -6506,11 +6506,11 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CUST_0572</t>
+          <t>CUST_0873</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004100000020116568</v>
       </c>
       <c r="C468" t="n">
         <v>0</v>
@@ -6519,11 +6519,11 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CUST_0567</t>
+          <t>CUST_0234</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C469" t="n">
         <v>0</v>
@@ -6532,11 +6532,11 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CUST_0560</t>
+          <t>CUST_0026</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C470" t="n">
         <v>0</v>
@@ -6545,11 +6545,11 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CUST_0558</t>
+          <t>CUST_0434</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C471" t="n">
         <v>0</v>
@@ -6558,11 +6558,11 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>CUST_0555</t>
+          <t>CUST_0899</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C472" t="n">
         <v>0</v>
@@ -6571,11 +6571,11 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CUST_0595</t>
+          <t>CUST_0066</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C473" t="n">
         <v>0</v>
@@ -6584,11 +6584,11 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CUST_0549</t>
+          <t>CUST_1128</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C474" t="n">
         <v>0</v>
@@ -6597,11 +6597,11 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CUST_0120</t>
+          <t>CUST_1182</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C475" t="n">
         <v>0</v>
@@ -6610,11 +6610,11 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CUST_0124</t>
+          <t>CUST_0102</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C476" t="n">
         <v>0</v>
@@ -6623,11 +6623,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CUST_0543</t>
+          <t>CUST_0488</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.004000000189989805</v>
       </c>
       <c r="C477" t="n">
         <v>0</v>
@@ -6636,11 +6636,11 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CUST_0542</t>
+          <t>CUST_1009</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003899999894201756</v>
       </c>
       <c r="C478" t="n">
         <v>0</v>
@@ -6649,11 +6649,11 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CUST_0129</t>
+          <t>CUST_0355</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003899999894201756</v>
       </c>
       <c r="C479" t="n">
         <v>0</v>
@@ -6662,11 +6662,11 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>CUST_0532</t>
+          <t>CUST_0010</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003899999894201756</v>
       </c>
       <c r="C480" t="n">
         <v>0</v>
@@ -6675,11 +6675,11 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CUST_0593</t>
+          <t>CUST_0096</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003899999894201756</v>
       </c>
       <c r="C481" t="n">
         <v>0</v>
@@ -6688,11 +6688,11 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>CUST_0111</t>
+          <t>CUST_0815</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003800000064074993</v>
       </c>
       <c r="C482" t="n">
         <v>0</v>
@@ -6701,11 +6701,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CUST_0677</t>
+          <t>CUST_0062</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003800000064074993</v>
       </c>
       <c r="C483" t="n">
         <v>0</v>
@@ -6714,11 +6714,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>CUST_0642</t>
+          <t>CUST_0283</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003800000064074993</v>
       </c>
       <c r="C484" t="n">
         <v>0</v>
@@ -6727,11 +6727,11 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CUST_0675</t>
+          <t>CUST_0628</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003700000001117587</v>
       </c>
       <c r="C485" t="n">
         <v>0</v>
@@ -6740,11 +6740,11 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>CUST_0098</t>
+          <t>CUST_0807</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003700000001117587</v>
       </c>
       <c r="C486" t="n">
         <v>0</v>
@@ -6753,11 +6753,11 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CUST_0664</t>
+          <t>CUST_0120</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003700000001117587</v>
       </c>
       <c r="C487" t="n">
         <v>0</v>
@@ -6766,11 +6766,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CUST_0660</t>
+          <t>CUST_1071</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003599999938160181</v>
       </c>
       <c r="C488" t="n">
         <v>0</v>
@@ -6779,11 +6779,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CUST_0656</t>
+          <t>CUST_0935</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003500000108033419</v>
       </c>
       <c r="C489" t="n">
         <v>0</v>
@@ -6792,11 +6792,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CUST_0651</t>
+          <t>CUST_0697</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003500000108033419</v>
       </c>
       <c r="C490" t="n">
         <v>0</v>
@@ -6805,11 +6805,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CUST_0649</t>
+          <t>CUST_0316</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003500000108033419</v>
       </c>
       <c r="C491" t="n">
         <v>0</v>
@@ -6818,11 +6818,11 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CUST_0636</t>
+          <t>CUST_0727</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003500000108033419</v>
       </c>
       <c r="C492" t="n">
         <v>0</v>
@@ -6831,11 +6831,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CUST_0001</t>
+          <t>CUST_1154</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003400000045076013</v>
       </c>
       <c r="C493" t="n">
         <v>0</v>
@@ -6844,11 +6844,11 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>CUST_0634</t>
+          <t>CUST_0995</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003299999982118607</v>
       </c>
       <c r="C494" t="n">
         <v>0</v>
@@ -6857,11 +6857,11 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>CUST_0628</t>
+          <t>CUST_0906</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003299999982118607</v>
       </c>
       <c r="C495" t="n">
         <v>0</v>
@@ -6870,11 +6870,11 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CUST_0627</t>
+          <t>CUST_0078</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003199999919161201</v>
       </c>
       <c r="C496" t="n">
         <v>0</v>
@@ -6883,11 +6883,11 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CUST_0102</t>
+          <t>CUST_0259</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003199999919161201</v>
       </c>
       <c r="C497" t="n">
         <v>0</v>
@@ -6896,11 +6896,11 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CUST_0621</t>
+          <t>CUST_0154</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003100000089034438</v>
       </c>
       <c r="C498" t="n">
         <v>0</v>
@@ -6909,11 +6909,11 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>CUST_0619</t>
+          <t>CUST_0647</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003100000089034438</v>
       </c>
       <c r="C499" t="n">
         <v>0</v>
@@ -6922,11 +6922,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CUST_0610</t>
+          <t>CUST_0359</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.003100000089034438</v>
       </c>
       <c r="C500" t="n">
         <v>0</v>
@@ -6935,11 +6935,11 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>CUST_1198</t>
+          <t>CUST_0685</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.3477999866008759</v>
+        <v>0.002700000070035458</v>
       </c>
       <c r="C501" t="n">
         <v>0</v>
